--- a/input/Basenotificar.xlsx
+++ b/input/Basenotificar.xlsx
@@ -1,37 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JULIANCHO ROBLES\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JULIANCHO ROBLES\Desktop\PROYECTOS GITHUB\oficios_notificaciones\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2933DEA7-7402-41AE-BAF1-F632CDE1BF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1B1201-E589-48BF-8D02-37E3DB322D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="query" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="query_1" localSheetId="0" hidden="1">query!$A$1:$W$61</definedName>
+    <definedName name="query__1_1" localSheetId="0" hidden="1">query!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" odcFile="C:\Users\JULIANCHO ROBLES\Downloads\query.iqy" keepAlive="1" name="query" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" odcFile="C:\Users\JULIANCHO ROBLES\Downloads\query (1).iqy" keepAlive="1" name="query (1)" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
     <dbPr connection="Provider=Microsoft.Office.List.OLEDB.2.0;Data Source=&quot;&quot;;ApplicationName=Excel;Version=12.0.0.0" command="&lt;LIST&gt;&lt;VIEWGUID&gt;E5C8D108-B3B4-420F-827F-40834FD7943F&lt;/VIEWGUID&gt;&lt;LISTNAME&gt;3a97168d-b7d6-4b2b-b4fd-34d0593d1f11&lt;/LISTNAME&gt;&lt;LISTWEB&gt;https://cargov.sharepoint.com/sites/NOTIFICACIONES2026/_vti_bin&lt;/LISTWEB&gt;&lt;LISTSUBWEB&gt;&lt;/LISTSUBWEB&gt;&lt;ROOTFOLDER&gt;&lt;/ROOTFOLDER&gt;&lt;/LIST&gt;" commandType="5"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="404">
   <si>
     <t>numero_expediente</t>
   </si>
@@ -391,9 +391,6 @@
   </si>
   <si>
     <t>Resolución No. 1387 de 31 de mayo de 2017</t>
-  </si>
-  <si>
-    <t>Ana Maria Garcia Rodriguez</t>
   </si>
   <si>
     <t>Por medio de la cual se decide un trámite administrativo ambiental de carácter sancionatorio y se adoptan otras determinaciones</t>
@@ -1251,7 +1248,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1729,11 +1726,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1875,7 +1870,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="query_1" backgroundRefresh="0" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="query__1_1" backgroundRefresh="0" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="24">
     <queryTableFields count="23">
       <queryTableField id="10" name="Notificador/Revisor" tableColumnId="1"/>
@@ -1907,32 +1902,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla_query_1" displayName="Tabla_query_1" ref="A1:W61" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:W61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_query__1_1" displayName="Tabla_query__1_1" ref="A1:W61" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:W61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
-    <tableColumn id="1" uniqueName="Notificador_x005f_x002f_Revisor" name="Notificador/Revisor" queryTableFieldId="10" dataDxfId="22"/>
-    <tableColumn id="2" uniqueName="Title" name="numero_expediente" queryTableFieldId="1" dataDxfId="21"/>
-    <tableColumn id="3" uniqueName="Regional" name="Regional" queryTableFieldId="4" dataDxfId="20"/>
-    <tableColumn id="4" uniqueName="EstadodelaActuacion" name="Estado de la Actuacion" queryTableFieldId="6" dataDxfId="19"/>
-    <tableColumn id="5" uniqueName="ACTUACION" name="ACTUACION" queryTableFieldId="2" dataDxfId="18"/>
-    <tableColumn id="6" uniqueName="NormaAplicable" name="Norma Aplicable" queryTableFieldId="5" dataDxfId="17"/>
-    <tableColumn id="7" uniqueName="Permisivo_x005f_x002f_Sancionatorio" name="Permisivo/Sancionatorio" queryTableFieldId="8" dataDxfId="16"/>
-    <tableColumn id="8" uniqueName="Recurso" name="Recurso" queryTableFieldId="7" dataDxfId="15"/>
-    <tableColumn id="9" uniqueName="Acto_Administrativo_No_y_fecha" name="Acto_Administrativo_No_y_fecha" queryTableFieldId="9" dataDxfId="14"/>
-    <tableColumn id="10" uniqueName="Recurso_actoadministrativo" name="Recurso_actoadministrativo" queryTableFieldId="21" dataDxfId="13"/>
-    <tableColumn id="11" uniqueName="Ordena" name="Ordena" queryTableFieldId="11" dataDxfId="12"/>
-    <tableColumn id="12" uniqueName="TipodeActoAdministrativo" name="Tipo de Acto Administrativo" queryTableFieldId="12" dataDxfId="11"/>
-    <tableColumn id="13" uniqueName="Funcionarioqueexpide" name="Funcionario que expide" queryTableFieldId="13" dataDxfId="10"/>
-    <tableColumn id="14" uniqueName="NombrePersona" name="Nombre Notificado" queryTableFieldId="3" dataDxfId="9"/>
-    <tableColumn id="15" uniqueName="Tipodedocumento" name="Tipo de documento" queryTableFieldId="14" dataDxfId="8"/>
-    <tableColumn id="16" uniqueName="NumeroDocumento" name="Numero Documento" queryTableFieldId="15" dataDxfId="7"/>
-    <tableColumn id="17" uniqueName="No_x005f_x002e_DireccionEfectiva" name="No. DireccionEfectiva" queryTableFieldId="20" dataDxfId="6"/>
-    <tableColumn id="18" uniqueName="AutorizaNotificacionelectr_x00f3" name="Autoriza Notificacion electrónica" queryTableFieldId="17" dataDxfId="5"/>
-    <tableColumn id="19" uniqueName="CorreoElectronico" name="Correo Electronico" queryTableFieldId="16" dataDxfId="4"/>
-    <tableColumn id="20" uniqueName="Radicadodeautorizaci_x005f_x00f3_nElec" name="Radicado de autorización Electronica" queryTableFieldId="18" dataDxfId="3"/>
-    <tableColumn id="21" uniqueName="Mododeenv_x005f_x00ed_o" name="Modo de envío" queryTableFieldId="19" dataDxfId="2"/>
-    <tableColumn id="22" uniqueName="FSObjType" name="Tipo de elemento" queryTableFieldId="23" dataDxfId="1"/>
-    <tableColumn id="23" uniqueName="FileDirRef" name="Ruta de acceso" queryTableFieldId="22" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="Notificador_x005f_x002f_Revisor" name="Notificador/Revisor" queryTableFieldId="10" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="Title" name="numero_expediente" queryTableFieldId="1" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="Regional" name="Regional" queryTableFieldId="4" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="EstadodelaActuacion" name="Estado de la Actuacion" queryTableFieldId="6" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="ACTUACION" name="ACTUACION" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="NormaAplicable" name="Norma Aplicable" queryTableFieldId="5" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="Permisivo_x005f_x002f_Sancionatorio" name="Permisivo/Sancionatorio" queryTableFieldId="8" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" uniqueName="Recurso" name="Recurso" queryTableFieldId="7" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" uniqueName="Acto_Administrativo_No_y_fecha" name="Acto_Administrativo_No_y_fecha" queryTableFieldId="9" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" uniqueName="Recurso_actoadministrativo" name="Recurso_actoadministrativo" queryTableFieldId="21" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" uniqueName="Ordena" name="Ordena" queryTableFieldId="11" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" uniqueName="TipodeActoAdministrativo" name="Tipo de Acto Administrativo" queryTableFieldId="12" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" uniqueName="Funcionarioqueexpide" name="Funcionario que expide" queryTableFieldId="13" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" uniqueName="NombrePersona" name="Nombre Notificado" queryTableFieldId="3" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" uniqueName="Tipodedocumento" name="Tipo de documento" queryTableFieldId="14" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" uniqueName="NumeroDocumento" name="Numero Documento" queryTableFieldId="15" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" uniqueName="No_x005f_x002e_DireccionEfectiva" name="No. DireccionEfectiva" queryTableFieldId="20" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" uniqueName="AutorizaNotificacionelectr_x00f3" name="Autoriza Notificacion electrónica" queryTableFieldId="17" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" uniqueName="CorreoElectronico" name="Correo Electronico" queryTableFieldId="16" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" uniqueName="Radicadodeautorizaci_x005f_x00f3_nElec" name="Radicado de autorización Electronica" queryTableFieldId="18" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" uniqueName="Mododeenv_x005f_x00ed_o" name="Modo de envío" queryTableFieldId="19" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" uniqueName="FSObjType" name="Tipo de elemento" queryTableFieldId="23" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" uniqueName="FileDirRef" name="Ruta de acceso" queryTableFieldId="22" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2234,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2338,7 +2333,7 @@
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2359,45 +2354,45 @@
       <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="3" t="b">
+      <c r="R2" t="b">
         <v>0</v>
       </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
       <c r="U2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2405,7 +2400,7 @@
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2426,45 +2421,45 @@
       <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="3" t="b">
+      <c r="R3" t="b">
         <v>0</v>
       </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="U3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2472,7 +2467,7 @@
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2493,45 +2488,45 @@
       <c r="H4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R4" s="3" t="b">
+      <c r="R4" t="b">
         <v>0</v>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
       <c r="U4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="V4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="W4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2539,7 +2534,7 @@
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2560,49 +2555,49 @@
       <c r="H5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R5" s="3" t="b">
+      <c r="R5" t="b">
         <v>1</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="S5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="T5" s="1" t="s">
         <v>61</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="V5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2610,7 +2605,7 @@
       <c r="A6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2631,47 +2626,47 @@
       <c r="H6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="R6" s="3" t="b">
+      <c r="R6" t="b">
         <v>0</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T6" s="2"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="V6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="W6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2679,7 +2674,7 @@
       <c r="A7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2700,49 +2695,49 @@
       <c r="H7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="1" t="s">
         <v>80</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R7" s="3" t="b">
+      <c r="R7" t="b">
         <v>1</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="S7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="V7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2750,7 +2745,7 @@
       <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2771,47 +2766,47 @@
       <c r="H8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="1" t="s">
         <v>90</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="R8" s="3" t="b">
+      <c r="R8" t="b">
         <v>1</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T8" s="2"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="V8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="W8" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2819,7 +2814,7 @@
       <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2840,47 +2835,47 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>100</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="1" t="s">
         <v>97</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R9" s="3" t="b">
+      <c r="R9" t="b">
         <v>1</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T9" s="2"/>
+      <c r="T9" s="1"/>
       <c r="U9" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="V9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2888,7 +2883,7 @@
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2909,45 +2904,45 @@
       <c r="H10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>110</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="1" t="s">
         <v>108</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="R10" s="3" t="b">
+      <c r="R10" t="b">
         <v>0</v>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
       <c r="U10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="V10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2955,7 +2950,7 @@
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -2976,53 +2971,53 @@
       <c r="H11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>110</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="1" t="s">
         <v>113</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q11" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="R11" s="3" t="b">
+      <c r="R11" t="b">
         <v>0</v>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
       <c r="U11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="V11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3043,45 +3038,45 @@
       <c r="H12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>121</v>
+      <c r="K12" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N12" s="2" t="s">
+      <c r="M12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>118</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="P12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="R12" s="3" t="b">
+      <c r="R12" t="b">
         <v>0</v>
       </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="V12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="W12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3089,7 +3084,7 @@
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -3110,45 +3105,45 @@
       <c r="H13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>121</v>
+      <c r="K13" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N13" s="2" t="s">
-        <v>125</v>
+      <c r="N13" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="P13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="R13" s="3" t="b">
+      <c r="R13" t="b">
         <v>0</v>
       </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
       <c r="U13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="V13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="W13" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3156,8 +3151,8 @@
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
+      <c r="B14" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>26</v>
@@ -3177,49 +3172,49 @@
       <c r="H14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>129</v>
+      <c r="M14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="P14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="R14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="U14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V14" s="2" t="s">
+      <c r="V14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="W14" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3227,8 +3222,8 @@
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>137</v>
+      <c r="B15" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>26</v>
@@ -3248,45 +3243,45 @@
       <c r="H15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>138</v>
+      <c r="M15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="P15" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R15" s="3" t="b">
+      <c r="R15" t="b">
         <v>0</v>
       </c>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
       <c r="U15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="V15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="W15" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3294,8 +3289,8 @@
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>144</v>
+      <c r="B16" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>26</v>
@@ -3315,57 +3310,57 @@
       <c r="H16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>145</v>
+      <c r="N16" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="P16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="R16" s="3" t="b">
+      <c r="R16" t="b">
         <v>0</v>
       </c>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
       <c r="U16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V16" s="2" t="s">
+      <c r="V16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="W16" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>67</v>
@@ -3382,67 +3377,67 @@
       <c r="H17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>158</v>
+      <c r="I17" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>154</v>
+      <c r="N17" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="P17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="R17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S17" s="2" t="s">
+      <c r="T17" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="U17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="V17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="W17" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>27</v>
@@ -3453,59 +3448,59 @@
       <c r="H18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="2" t="s">
-        <v>166</v>
+      <c r="N18" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="P18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Q18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="R18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="1"/>
+      <c r="U18" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="T18" s="2"/>
-      <c r="U18" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="V18" s="2" t="s">
+      <c r="V18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="W18" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>174</v>
+        <v>156</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>67</v>
@@ -3522,57 +3517,57 @@
       <c r="H19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>175</v>
+      <c r="M19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="P19" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="Q19" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="R19" s="3" t="b">
+      <c r="R19" t="b">
         <v>1</v>
       </c>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
       <c r="U19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V19" s="2" t="s">
+      <c r="V19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="W19" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>182</v>
+        <v>156</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>67</v>
@@ -3589,45 +3584,45 @@
       <c r="H20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>183</v>
+      <c r="N20" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="P20" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="R20" s="3" t="b">
+      <c r="R20" t="b">
         <v>0</v>
       </c>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
       <c r="U20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V20" s="2" t="s">
+      <c r="V20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="W20" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3635,8 +3630,8 @@
       <c r="A21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>188</v>
+      <c r="B21" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>66</v>
@@ -3645,7 +3640,7 @@
         <v>67</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>27</v>
@@ -3656,45 +3651,45 @@
       <c r="H21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J21" s="2" t="s">
+      <c r="I21" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>131</v>
+      <c r="K21" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>190</v>
+      <c r="M21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="P21" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="R21" s="3" t="b">
+      <c r="R21" t="b">
         <v>0</v>
       </c>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
       <c r="U21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V21" s="2" t="s">
+      <c r="V21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="W21" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3702,8 +3697,8 @@
       <c r="A22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>188</v>
+      <c r="B22" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>66</v>
@@ -3712,7 +3707,7 @@
         <v>67</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>27</v>
@@ -3723,45 +3718,45 @@
       <c r="H22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="I22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>131</v>
+      <c r="K22" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>195</v>
+      <c r="M22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="P22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="R22" s="3" t="b">
+      <c r="R22" t="b">
         <v>0</v>
       </c>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
       <c r="U22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V22" s="2" t="s">
+      <c r="V22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="W22" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3769,8 +3764,8 @@
       <c r="A23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>188</v>
+      <c r="B23" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>66</v>
@@ -3790,45 +3785,45 @@
       <c r="H23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="J23" s="2" t="s">
+      <c r="I23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>131</v>
+      <c r="K23" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>199</v>
+      <c r="M23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="P23" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q23" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="R23" s="3" t="b">
+      <c r="R23" t="b">
         <v>0</v>
       </c>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
       <c r="U23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="V23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="W23" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3836,8 +3831,8 @@
       <c r="A24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>202</v>
+      <c r="B24" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>66</v>
@@ -3857,47 +3852,47 @@
       <c r="H24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="J24" s="2" t="s">
+      <c r="I24" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>131</v>
+      <c r="K24" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>203</v>
+      <c r="M24" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="P24" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="Q24" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="R24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="T24" s="2"/>
+      <c r="T24" s="1"/>
       <c r="U24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V24" s="2" t="s">
+      <c r="V24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="W24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3905,8 +3900,8 @@
       <c r="A25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>202</v>
+      <c r="B25" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>66</v>
@@ -3926,47 +3921,47 @@
       <c r="H25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>131</v>
+      <c r="I25" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>209</v>
+      <c r="M25" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="P25" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="Q25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="T25" s="2"/>
+      <c r="T25" s="1"/>
       <c r="U25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V25" s="2" t="s">
+      <c r="V25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W25" s="2" t="s">
+      <c r="W25" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3974,8 +3969,8 @@
       <c r="A26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>214</v>
+      <c r="B26" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>66</v>
@@ -3984,7 +3979,7 @@
         <v>67</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>27</v>
@@ -3995,45 +3990,45 @@
       <c r="H26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>215</v>
+      <c r="M26" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="P26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q26" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="Q26" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="R26" s="3" t="b">
+      <c r="R26" t="b">
         <v>0</v>
       </c>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
       <c r="U26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V26" s="2" t="s">
+      <c r="V26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="W26" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4041,8 +4036,8 @@
       <c r="A27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>220</v>
+      <c r="B27" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>81</v>
@@ -4062,49 +4057,49 @@
       <c r="H27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>221</v>
+      <c r="N27" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="P27" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27" s="2" t="s">
+      <c r="T27" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="U27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V27" s="2" t="s">
+      <c r="V27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="W27" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4112,8 +4107,8 @@
       <c r="A28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>214</v>
+      <c r="B28" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>66</v>
@@ -4122,7 +4117,7 @@
         <v>67</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>27</v>
@@ -4133,45 +4128,45 @@
       <c r="H28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J28" s="2" t="s">
+      <c r="I28" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>217</v>
+      <c r="K28" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>228</v>
+      <c r="M28" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="P28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q28" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="R28" s="3" t="b">
+      <c r="R28" t="b">
         <v>0</v>
       </c>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
       <c r="U28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V28" s="2" t="s">
+      <c r="V28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4179,17 +4174,17 @@
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>214</v>
+      <c r="B29" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>27</v>
@@ -4200,45 +4195,45 @@
       <c r="H29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="I29" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>217</v>
+      <c r="K29" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>232</v>
+      <c r="M29" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="P29" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="Q29" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="R29" s="3" t="b">
+      <c r="R29" t="b">
         <v>0</v>
       </c>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
       <c r="U29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V29" s="2" t="s">
+      <c r="V29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4246,8 +4241,8 @@
       <c r="A30" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>235</v>
+      <c r="B30" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>66</v>
@@ -4256,7 +4251,7 @@
         <v>67</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>27</v>
@@ -4267,45 +4262,45 @@
       <c r="H30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K30" s="2" t="s">
+      <c r="I30" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>236</v>
+      <c r="M30" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="P30" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q30" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="Q30" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="R30" s="3" t="b">
+      <c r="R30" t="b">
         <v>0</v>
       </c>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
       <c r="U30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V30" s="2" t="s">
+      <c r="V30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="W30" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4313,8 +4308,8 @@
       <c r="A31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>242</v>
+      <c r="B31" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>66</v>
@@ -4323,7 +4318,7 @@
         <v>67</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>27</v>
@@ -4334,45 +4329,45 @@
       <c r="H31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>244</v>
+      <c r="M31" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="P31" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q31" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="R31" s="3" t="b">
+      <c r="R31" t="b">
         <v>0</v>
       </c>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
       <c r="U31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V31" s="2" t="s">
+      <c r="V31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="W31" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4380,8 +4375,8 @@
       <c r="A32" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>242</v>
+      <c r="B32" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>66</v>
@@ -4390,7 +4385,7 @@
         <v>67</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>27</v>
@@ -4401,47 +4396,47 @@
       <c r="H32" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>250</v>
+      <c r="M32" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="P32" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="Q32" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="R32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="T32" s="2"/>
+      <c r="T32" s="1"/>
       <c r="U32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V32" s="2" t="s">
+      <c r="V32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W32" s="2" t="s">
+      <c r="W32" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4449,8 +4444,8 @@
       <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>242</v>
+      <c r="B33" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>66</v>
@@ -4459,7 +4454,7 @@
         <v>67</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>27</v>
@@ -4470,47 +4465,47 @@
       <c r="H33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>254</v>
+      <c r="M33" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="P33" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="Q33" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="R33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="T33" s="2"/>
+      <c r="T33" s="1"/>
       <c r="U33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V33" s="2" t="s">
+      <c r="V33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W33" s="2" t="s">
+      <c r="W33" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4518,8 +4513,8 @@
       <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>242</v>
+      <c r="B34" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>66</v>
@@ -4528,7 +4523,7 @@
         <v>67</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>27</v>
@@ -4539,47 +4534,47 @@
       <c r="H34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>258</v>
+      <c r="M34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="P34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="Q34" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="R34" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="T34" s="2"/>
+      <c r="T34" s="1"/>
       <c r="U34" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V34" s="2" t="s">
+      <c r="V34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W34" s="2" t="s">
+      <c r="W34" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4587,8 +4582,8 @@
       <c r="A35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>242</v>
+      <c r="B35" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>66</v>
@@ -4608,47 +4603,47 @@
       <c r="H35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>209</v>
+      <c r="M35" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="P35" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="Q35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="T35" s="2"/>
+      <c r="T35" s="1"/>
       <c r="U35" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V35" s="2" t="s">
+      <c r="V35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W35" s="2" t="s">
+      <c r="W35" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4656,8 +4651,8 @@
       <c r="A36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>220</v>
+      <c r="B36" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>81</v>
@@ -4666,7 +4661,7 @@
         <v>67</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>27</v>
@@ -4677,45 +4672,45 @@
       <c r="H36" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N36" s="2" t="s">
-        <v>265</v>
+      <c r="N36" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="P36" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q36" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="Q36" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="R36" s="3" t="b">
+      <c r="R36" t="b">
         <v>0</v>
       </c>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
       <c r="U36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V36" s="2" t="s">
+      <c r="V36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W36" s="2" t="s">
+      <c r="W36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4723,8 +4718,8 @@
       <c r="A37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>268</v>
+      <c r="B37" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>81</v>
@@ -4733,7 +4728,7 @@
         <v>67</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>27</v>
@@ -4744,47 +4739,47 @@
       <c r="H37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>269</v>
+      <c r="N37" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="P37" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="Q37" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="R37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="T37" s="2"/>
+      <c r="T37" s="1"/>
       <c r="U37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V37" s="2" t="s">
+      <c r="V37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W37" s="2" t="s">
+      <c r="W37" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4792,8 +4787,8 @@
       <c r="A38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>275</v>
+      <c r="B38" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>26</v>
@@ -4805,7 +4800,7 @@
         <v>107</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>29</v>
@@ -4813,45 +4808,45 @@
       <c r="H38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M38" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>276</v>
+      <c r="N38" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="P38" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q38" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="R38" s="3" t="b">
+      <c r="R38" t="b">
         <v>0</v>
       </c>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
       <c r="U38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V38" s="2" t="s">
+      <c r="V38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W38" s="2" t="s">
+      <c r="W38" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4859,8 +4854,8 @@
       <c r="A39" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>282</v>
+      <c r="B39" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>26</v>
@@ -4880,49 +4875,49 @@
       <c r="H39" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J39" s="2" t="s">
+      <c r="I39" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="K39" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="M39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>283</v>
+      <c r="N39" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P39" s="2" t="s">
+      <c r="P39" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="Q39" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="R39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" s="2" t="s">
+      <c r="T39" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="U39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V39" s="2" t="s">
+      <c r="V39" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W39" s="2" t="s">
+      <c r="W39" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4930,8 +4925,8 @@
       <c r="A40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>282</v>
+      <c r="B40" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>26</v>
@@ -4951,47 +4946,47 @@
       <c r="H40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J40" s="2" t="s">
+      <c r="I40" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="K40" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="M40" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>289</v>
+      <c r="N40" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P40" s="2" t="s">
+      <c r="P40" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q40" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="R40" s="3" t="b">
+      <c r="Q40" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="R40" t="b">
         <v>0</v>
       </c>
-      <c r="S40" s="2" t="s">
+      <c r="S40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T40" s="2"/>
+      <c r="T40" s="1"/>
       <c r="U40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V40" s="2" t="s">
+      <c r="V40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W40" s="2" t="s">
+      <c r="W40" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4999,8 +4994,8 @@
       <c r="A41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>291</v>
+      <c r="B41" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>26</v>
@@ -5020,49 +5015,49 @@
       <c r="H41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J41" s="2" t="s">
+      <c r="I41" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>131</v>
+      <c r="K41" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>292</v>
+      <c r="M41" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P41" s="2" t="s">
+      <c r="P41" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="Q41" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="R41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S41" s="2" t="s">
+      <c r="T41" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="U41" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V41" s="2" t="s">
+      <c r="V41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W41" s="2" t="s">
+      <c r="W41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5070,8 +5065,8 @@
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>299</v>
+      <c r="B42" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>81</v>
@@ -5083,7 +5078,7 @@
         <v>79</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>29</v>
@@ -5091,49 +5086,49 @@
       <c r="H42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J42" s="2" t="s">
+      <c r="I42" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>279</v>
+      <c r="K42" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="M42" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N42" s="2" t="s">
-        <v>300</v>
+      <c r="N42" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P42" s="2" t="s">
+      <c r="P42" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
+      <c r="S42" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="Q42" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="R42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" s="2" t="s">
+      <c r="T42" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="U42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V42" s="2" t="s">
+      <c r="V42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W42" s="2" t="s">
+      <c r="W42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5141,8 +5136,8 @@
       <c r="A43" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>299</v>
+      <c r="B43" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>81</v>
@@ -5154,7 +5149,7 @@
         <v>79</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>29</v>
@@ -5162,49 +5157,49 @@
       <c r="H43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J43" s="2" t="s">
+      <c r="I43" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>279</v>
+      <c r="K43" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M43" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N43" s="2" t="s">
-        <v>307</v>
+      <c r="N43" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P43" s="2" t="s">
+      <c r="P43" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="Q43" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="R43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" s="2" t="s">
+      <c r="T43" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="U43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V43" s="2" t="s">
+      <c r="V43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W43" s="2" t="s">
+      <c r="W43" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5212,8 +5207,8 @@
       <c r="A44" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>313</v>
+      <c r="B44" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>26</v>
@@ -5233,61 +5228,61 @@
       <c r="H44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="I44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="M44" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N44" s="2" t="s">
-        <v>314</v>
+      <c r="N44" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P44" s="2" t="s">
+      <c r="P44" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="Q44" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="R44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S44" s="2" t="s">
+      <c r="T44" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="U44" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V44" s="2" t="s">
+      <c r="V44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W44" s="2" t="s">
+      <c r="W44" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>321</v>
+        <v>156</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>67</v>
@@ -5304,57 +5299,57 @@
       <c r="H45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="M45" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>322</v>
+      <c r="N45" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P45" s="2" t="s">
+      <c r="P45" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q45" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="Q45" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="R45" s="3" t="b">
+      <c r="R45" t="b">
         <v>0</v>
       </c>
-      <c r="S45" s="2"/>
-      <c r="T45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
       <c r="U45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V45" s="2" t="s">
+      <c r="V45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W45" s="2" t="s">
+      <c r="W45" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>327</v>
+        <v>156</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>67</v>
@@ -5371,63 +5366,63 @@
       <c r="H46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>328</v>
+      <c r="M46" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="P46" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q46" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="Q46" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="R46" s="3" t="b">
+      <c r="R46" t="b">
         <v>0</v>
       </c>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
       <c r="U46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V46" s="2" t="s">
+      <c r="V46" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W46" s="2" t="s">
+      <c r="W46" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>333</v>
+        <v>156</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>27</v>
@@ -5438,45 +5433,45 @@
       <c r="H47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>185</v>
+      <c r="I47" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="M47" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N47" s="2" t="s">
-        <v>334</v>
+      <c r="N47" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P47" s="2" t="s">
+      <c r="P47" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q47" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="Q47" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="R47" s="3" t="b">
+      <c r="R47" t="b">
         <v>0</v>
       </c>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
       <c r="U47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V47" s="2" t="s">
+      <c r="V47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W47" s="2" t="s">
+      <c r="W47" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5484,8 +5479,8 @@
       <c r="A48" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>338</v>
+      <c r="B48" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>26</v>
@@ -5505,45 +5500,45 @@
       <c r="H48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J48" s="2" t="s">
+      <c r="I48" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K48" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="M48" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N48" s="2" t="s">
-        <v>339</v>
+      <c r="N48" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P48" s="2" t="s">
+      <c r="P48" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q48" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="Q48" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="R48" s="3" t="b">
+      <c r="R48" t="b">
         <v>0</v>
       </c>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
       <c r="U48" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V48" s="2" t="s">
+      <c r="V48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W48" s="2" t="s">
+      <c r="W48" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5551,8 +5546,8 @@
       <c r="A49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>343</v>
+      <c r="B49" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>26</v>
@@ -5572,49 +5567,49 @@
       <c r="H49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K49" s="2" t="s">
+      <c r="I49" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="M49" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N49" s="2" t="s">
-        <v>344</v>
+      <c r="N49" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P49" s="2" t="s">
+      <c r="P49" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="Q49" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="R49" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S49" s="2" t="s">
+      <c r="T49" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="U49" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V49" s="2" t="s">
+      <c r="V49" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W49" s="2" t="s">
+      <c r="W49" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5622,8 +5617,8 @@
       <c r="A50" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>351</v>
+      <c r="B50" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>26</v>
@@ -5643,45 +5638,45 @@
       <c r="H50" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="I50" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>131</v>
+      <c r="K50" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>352</v>
+      <c r="M50" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P50" s="2" t="s">
+      <c r="P50" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q50" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="Q50" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="R50" s="3" t="b">
+      <c r="R50" t="b">
         <v>0</v>
       </c>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
       <c r="U50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V50" s="2" t="s">
+      <c r="V50" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W50" s="2" t="s">
+      <c r="W50" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5689,8 +5684,8 @@
       <c r="A51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>356</v>
+      <c r="B51" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>26</v>
@@ -5702,7 +5697,7 @@
         <v>117</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>29</v>
@@ -5710,45 +5705,45 @@
       <c r="H51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M51" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N51" s="2" t="s">
-        <v>357</v>
+      <c r="N51" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P51" s="2" t="s">
+      <c r="P51" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q51" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="Q51" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="R51" s="3" t="b">
+      <c r="R51" t="b">
         <v>0</v>
       </c>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
       <c r="U51" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V51" s="2" t="s">
+      <c r="V51" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W51" s="2" t="s">
+      <c r="W51" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5756,8 +5751,8 @@
       <c r="A52" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>362</v>
+      <c r="B52" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>26</v>
@@ -5769,7 +5764,7 @@
         <v>117</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>29</v>
@@ -5777,45 +5772,45 @@
       <c r="H52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J52" s="2" t="s">
+      <c r="I52" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>279</v>
+      <c r="K52" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="M52" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N52" s="2" t="s">
-        <v>363</v>
+      <c r="N52" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P52" s="2" t="s">
+      <c r="P52" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q52" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="Q52" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="R52" s="3" t="b">
+      <c r="R52" t="b">
         <v>0</v>
       </c>
-      <c r="S52" s="2"/>
-      <c r="T52" s="2"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
       <c r="U52" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V52" s="2" t="s">
+      <c r="V52" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W52" s="2" t="s">
+      <c r="W52" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5823,8 +5818,8 @@
       <c r="A53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>367</v>
+      <c r="B53" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>26</v>
@@ -5844,47 +5839,47 @@
       <c r="H53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="I53" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="M53" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N53" s="2" t="s">
-        <v>368</v>
+      <c r="N53" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P53" s="2" t="s">
+      <c r="P53" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="Q53" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="R53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="T53" s="2"/>
+      <c r="T53" s="1"/>
       <c r="U53" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V53" s="2" t="s">
+      <c r="V53" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W53" s="2" t="s">
+      <c r="W53" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5892,8 +5887,8 @@
       <c r="A54" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>374</v>
+      <c r="B54" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>26</v>
@@ -5913,45 +5908,45 @@
       <c r="H54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>376</v>
+      <c r="I54" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M54" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="N54" s="2" t="s">
+      <c r="M54" s="1" t="s">
         <v>375</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="P54" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q54" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="Q54" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="R54" s="3" t="b">
+      <c r="R54" t="b">
         <v>0</v>
       </c>
-      <c r="S54" s="2"/>
-      <c r="T54" s="2"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
       <c r="U54" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V54" s="2" t="s">
+      <c r="V54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W54" s="2" t="s">
+      <c r="W54" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5959,8 +5954,8 @@
       <c r="A55" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>374</v>
+      <c r="B55" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>26</v>
@@ -5980,45 +5975,45 @@
       <c r="H55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J55" s="2" t="s">
+      <c r="I55" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>376</v>
+      <c r="K55" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M55" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>380</v>
+      <c r="M55" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P55" s="2" t="s">
+      <c r="P55" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q55" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="Q55" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="R55" s="3" t="b">
+      <c r="R55" t="b">
         <v>0</v>
       </c>
-      <c r="S55" s="2"/>
-      <c r="T55" s="2"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
       <c r="U55" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V55" s="2" t="s">
+      <c r="V55" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W55" s="2" t="s">
+      <c r="W55" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6026,8 +6021,8 @@
       <c r="A56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>374</v>
+      <c r="B56" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>26</v>
@@ -6047,45 +6042,45 @@
       <c r="H56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J56" s="2" t="s">
+      <c r="I56" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>131</v>
+      <c r="K56" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M56" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="N56" s="2" t="s">
+      <c r="M56" s="1" t="s">
         <v>383</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P56" s="2" t="s">
+      <c r="P56" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q56" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="Q56" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R56" s="3" t="b">
+      <c r="R56" t="b">
         <v>0</v>
       </c>
-      <c r="S56" s="2"/>
-      <c r="T56" s="2"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
       <c r="U56" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V56" s="2" t="s">
+      <c r="V56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W56" s="2" t="s">
+      <c r="W56" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6093,8 +6088,8 @@
       <c r="A57" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>374</v>
+      <c r="B57" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>26</v>
@@ -6114,45 +6109,45 @@
       <c r="H57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J57" s="2" t="s">
+      <c r="I57" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>131</v>
+      <c r="K57" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M57" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>387</v>
+      <c r="M57" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P57" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q57" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R57" s="3" t="b">
+      <c r="P57" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="R57" t="b">
         <v>0</v>
       </c>
-      <c r="S57" s="2"/>
-      <c r="T57" s="2"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
       <c r="U57" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V57" s="2" t="s">
+      <c r="V57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W57" s="2" t="s">
+      <c r="W57" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6160,8 +6155,8 @@
       <c r="A58" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>374</v>
+      <c r="B58" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>26</v>
@@ -6181,45 +6176,45 @@
       <c r="H58" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J58" s="2" t="s">
+      <c r="I58" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>131</v>
+      <c r="K58" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>389</v>
+      <c r="M58" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P58" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q58" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R58" s="3" t="b">
+      <c r="P58" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="R58" t="b">
         <v>0</v>
       </c>
-      <c r="S58" s="2"/>
-      <c r="T58" s="2"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
       <c r="U58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V58" s="2" t="s">
+      <c r="V58" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W58" s="2" t="s">
+      <c r="W58" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6227,8 +6222,8 @@
       <c r="A59" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>374</v>
+      <c r="B59" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>26</v>
@@ -6248,45 +6243,45 @@
       <c r="H59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J59" s="2" t="s">
+      <c r="I59" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>131</v>
+      <c r="K59" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M59" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N59" s="2" t="s">
-        <v>391</v>
+      <c r="M59" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P59" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="R59" s="3" t="b">
+      <c r="P59" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="R59" t="b">
         <v>0</v>
       </c>
-      <c r="S59" s="2"/>
-      <c r="T59" s="2"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
       <c r="U59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V59" s="2" t="s">
+      <c r="V59" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W59" s="2" t="s">
+      <c r="W59" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6294,8 +6289,8 @@
       <c r="A60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>374</v>
+      <c r="B60" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>26</v>
@@ -6315,45 +6310,45 @@
       <c r="H60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I60" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="J60" s="2" t="s">
+      <c r="I60" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>131</v>
+      <c r="K60" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M60" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>393</v>
+      <c r="M60" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P60" s="2" t="s">
+      <c r="P60" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q60" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="Q60" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="R60" s="3" t="b">
+      <c r="R60" t="b">
         <v>1</v>
       </c>
-      <c r="S60" s="2"/>
-      <c r="T60" s="2"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
       <c r="U60" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V60" s="2" t="s">
+      <c r="V60" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W60" s="2" t="s">
+      <c r="W60" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6361,8 +6356,8 @@
       <c r="A61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>397</v>
+      <c r="B61" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>26</v>
@@ -6382,49 +6377,49 @@
       <c r="H61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="M61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N61" s="2" t="s">
-        <v>398</v>
+      <c r="N61" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P61" s="2" t="s">
+      <c r="P61" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
+      <c r="S61" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="Q61" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="R61" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S61" s="2" t="s">
+      <c r="T61" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="T61" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="U61" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="V61" s="2" t="s">
+      <c r="V61" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W61" s="2" t="s">
+      <c r="W61" s="1" t="s">
         <v>40</v>
       </c>
     </row>
